--- a/data/party_colors.xlsx
+++ b/data/party_colors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D742A1-7873-482F-A3A4-3868F085BFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20185429-9163-4327-8BCE-671AFEE3AD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="145">
   <si>
     <t>country_name</t>
   </si>
@@ -465,6 +465,9 @@
   </si>
   <si>
     <t>PARTIDO ENCUENTRO SOCIAL</t>
+  </si>
+  <si>
+    <t>PARTIDO INDEPENDIENTE</t>
   </si>
 </sst>
 </file>
@@ -807,8 +810,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J85"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J86"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="109" bestFit="1" customWidth="1"/>
   </cols>
@@ -3533,6 +3536,17 @@
         <v>16</v>
       </c>
     </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>58</v>
+      </c>
+      <c r="B86" t="s">
+        <v>144</v>
+      </c>
+      <c r="J86" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/party_colors.xlsx
+++ b/data/party_colors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20185429-9163-4327-8BCE-671AFEE3AD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D9C659-5F78-4568-8B33-6B4FF48D27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="153">
   <si>
     <t>country_name</t>
   </si>
@@ -468,6 +468,30 @@
   </si>
   <si>
     <t>PARTIDO INDEPENDIENTE</t>
+  </si>
+  <si>
+    <t>#C8102E</t>
+  </si>
+  <si>
+    <t>#0033A0</t>
+  </si>
+  <si>
+    <t>#FFDE00</t>
+  </si>
+  <si>
+    <t>#800000</t>
+  </si>
+  <si>
+    <t>#F37A1F</t>
+  </si>
+  <si>
+    <t>#009639</t>
+  </si>
+  <si>
+    <t>#702F8A</t>
+  </si>
+  <si>
+    <t>#7F7F7F</t>
   </si>
 </sst>
 </file>
@@ -3341,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="J79" t="s">
-        <v>10</v>
+        <v>145</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -3373,7 +3397,7 @@
         <v>0.363736404182193</v>
       </c>
       <c r="J80" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -3405,7 +3429,7 @@
         <v>0.19494955169334199</v>
       </c>
       <c r="J81" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -3437,7 +3461,7 @@
         <v>0.184818149999428</v>
       </c>
       <c r="J82" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -3469,7 +3493,7 @@
         <v>2.84169297099683E-2</v>
       </c>
       <c r="J83" t="s">
-        <v>14</v>
+        <v>149</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -3501,7 +3525,7 @@
         <v>1.2295779976539901E-2</v>
       </c>
       <c r="J84" t="s">
-        <v>15</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -3533,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="s">
-        <v>16</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -3544,7 +3568,7 @@
         <v>144</v>
       </c>
       <c r="J86" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/data/party_colors.xlsx
+++ b/data/party_colors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D9C659-5F78-4568-8B33-6B4FF48D27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0EE5BE-4849-4ABC-9604-4E56F94B8C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -837,7 +837,16 @@
   <dimension ref="A1:J86"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="109" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
